--- a/data/travel_vouchers.xlsx
+++ b/data/travel_vouchers.xlsx
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1599,7 +1599,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T20260305009</t>
+          <t>T20260310001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1620,12 +1620,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-10T09:41:23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-10T09:41:23</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-10T09:41:23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-10T09:41:23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T20260305008</t>
+          <t>T20260305009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1708,12 +1708,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T20260305007</t>
+          <t>T20260305008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1796,12 +1796,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T20260305006</t>
+          <t>T20260305007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1884,12 +1884,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T20260305005</t>
+          <t>T20260305006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1972,12 +1972,12 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T20260305004</t>
+          <t>T20260305005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2060,12 +2060,12 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T20260305003</t>
+          <t>T20260305004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2148,12 +2148,12 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T20260305002</t>
+          <t>T20260305003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2236,12 +2236,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T20260305001</t>
+          <t>T20260305002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2324,12 +2324,12 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T20260303002</t>
+          <t>T20260305001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2402,7 +2402,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2412,12 +2412,12 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-03T08:00:00</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03T17:00:00</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-03-03T17:22:41</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-03-03T17:22:41</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T20260302002</t>
+          <t>T20260303002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2500,12 +2500,12 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-03T08:00:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-03T17:00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-03T17:22:41</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-03T17:22:41</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T20260302001</t>
+          <t>T20260302002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2581,35 +2581,19 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>施品甄</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>115CA008</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>專家會議</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>台南 台北</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-02T07:30:00</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-02T18:00:00</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2634,17 +2618,17 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[{"date_md": "2026-03-02", "route": "台南 台北", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 250, "accommodation_amt": 0, "other_amt": 180, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北車站 IEAT", "transport_type": "計程車", "transport_amt": 225, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北 台南", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2653,55 +2637,67 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>["data\\attachments\\T20260302001\\高鐵.pdf"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-03-02T11:36:20</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-03-05T11:08:01</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>2026-03-02T11:43:53</t>
-        </is>
-      </c>
+          <t>2026-03-02T17:58:06</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T20260226001</t>
+          <t>T20260302001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deleted</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>施品甄</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>專家會議</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>台南 台北</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:00</t>
+          <t>2026-03-02T07:30:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:00</t>
+          <t>2026-03-02T18:00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2726,17 +2722,17 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"date_md": "2026-03-02", "route": "台南 台北", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 250, "accommodation_amt": 0, "other_amt": 180, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北車站 IEAT", "transport_type": "計程車", "transport_amt": 225, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北 台南", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}]</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2745,25 +2741,29 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>["data\\attachments\\T20260226001\\高鐵.pdf"]</t>
+          <t>["data\\attachments\\T20260302001\\高鐵.pdf"]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:19</t>
+          <t>2026-03-02T11:36:20</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-03-02T11:49:55</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+          <t>2026-03-05T11:08:01</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:43:53</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T20260225002</t>
+          <t>T20260226001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2774,7 +2774,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-26T12:05:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-26T12:05:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2797,48 +2797,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
@@ -2861,17 +2833,17 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["data\\attachments\\T20260226001\\高鐵.pdf"]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-26T12:05:19</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-03-02T16:37:45</t>
+          <t>2026-03-02T11:49:55</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
@@ -2879,12 +2851,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T20260225001</t>
+          <t>T20260225002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2893,35 +2865,19 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>施品甄</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>115CA008</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>工作會議</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>台南 板橋</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-02-25T07:00:00</t>
+          <t>2026-02-25T13:01:41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-25T18:15:00</t>
+          <t>2026-02-25T13:01:41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2931,18 +2887,18 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2953,22 +2909,22 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2979,12 +2935,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[{"date_md": "02/25", "route": "台南 板橋", "transport_type": "高鐵", "transport_amt": 1320.0, "per_diem_amt": 0.0, "accommodation_amt": 0.0, "other_amt": 0.0, "receipt_no": ""}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1320.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2993,20 +2949,152 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-02-25T13:01:41</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2026-03-02T16:37:45</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T20260225001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>施品甄</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>工作會議</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台南 板橋</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-02-25T07:00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-02-25T18:15:00</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>[{"date_md": "02/25", "route": "台南 板橋", "transport_type": "高鐵", "transport_amt": 1320.0, "per_diem_amt": 0.0, "accommodation_amt": 0.0, "other_amt": 0.0, "receipt_no": ""}]</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1320.0</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>["data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf"]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>2026-02-25T12:58:44</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>2026-02-25T14:58:41</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/travel_vouchers.xlsx
+++ b/data/travel_vouchers.xlsx
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH18"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1599,7 +1599,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T20260310001</t>
+          <t>T20260305009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1620,12 +1620,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-10T09:41:23</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-10T09:41:23</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-03-10T09:41:23</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-03-10T09:41:23</t>
+          <t>2026-03-05T12:04:05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T20260305009</t>
+          <t>T20260305008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1708,12 +1708,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:05</t>
+          <t>2026-03-05T12:03:46</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T20260305008</t>
+          <t>T20260305007</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1796,12 +1796,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:46</t>
+          <t>2026-03-05T12:03:42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T20260305007</t>
+          <t>T20260305006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1884,12 +1884,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-03-05T12:03:42</t>
+          <t>2026-03-05T11:50:50</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T20260305006</t>
+          <t>T20260305005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1972,12 +1972,12 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:50</t>
+          <t>2026-03-05T11:38:39</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T20260305005</t>
+          <t>T20260305004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2060,12 +2060,12 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-03-05T11:38:39</t>
+          <t>2026-03-05T11:31:03</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T20260305004</t>
+          <t>T20260305003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2148,12 +2148,12 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-03-05T11:31:03</t>
+          <t>2026-03-05T11:30:55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T20260305003</t>
+          <t>T20260305002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2236,12 +2236,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-03-05T11:30:55</t>
+          <t>2026-03-05T11:16:01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T20260305002</t>
+          <t>T20260305001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2324,12 +2324,12 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:16:01</t>
+          <t>2026-03-05T11:06:30</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T20260305001</t>
+          <t>T20260303002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2402,7 +2402,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2412,12 +2412,12 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-03T08:00:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-03T17:00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-03T17:22:41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-03-05T11:06:30</t>
+          <t>2026-03-03T17:22:41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T20260303002</t>
+          <t>T20260302002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2500,12 +2500,12 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-03T08:00:00</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-03T17:00:00</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-03-03T17:22:41</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-03-03T17:22:41</t>
+          <t>2026-03-02T17:58:06</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T20260302002</t>
+          <t>T20260302001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2581,19 +2581,35 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>施品甄</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>專家會議</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>台南 台北</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-02T07:30:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-02T18:00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2618,17 +2634,17 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"date_md": "2026-03-02", "route": "台南 台北", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 250, "accommodation_amt": 0, "other_amt": 180, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北車站 IEAT", "transport_type": "計程車", "transport_amt": 225, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北 台南", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}]</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2637,67 +2653,55 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["data\\attachments\\T20260302001\\高鐵.pdf"]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
+          <t>2026-03-02T11:36:20</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-03-02T17:58:06</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+          <t>2026-03-05T11:08:01</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:43:53</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T20260302001</t>
+          <t>T20260226001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>施品甄</t>
-        </is>
-      </c>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>115CA008</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>專家會議</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>台南 台北</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-02T07:30:00</t>
+          <t>2026-02-26T12:05:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-02T18:00:00</t>
+          <t>2026-02-26T12:05:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2722,17 +2726,17 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[{"date_md": "2026-03-02", "route": "台南 台北", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 250, "accommodation_amt": 0, "other_amt": 180, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北車站 IEAT", "transport_type": "計程車", "transport_amt": 225, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}, {"date_md": "2026-03-02", "route": "台北 台南", "transport_type": "高鐵", "transport_amt": 1350, "per_diem_amt": 0, "accommodation_amt": 0, "other_amt": 0, "receipt_no": ""}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2741,29 +2745,25 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>["data\\attachments\\T20260302001\\高鐵.pdf"]</t>
+          <t>["data\\attachments\\T20260226001\\高鐵.pdf"]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-03-02T11:36:20</t>
+          <t>2026-02-26T12:05:19</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-03-05T11:08:01</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>2026-03-02T11:43:53</t>
-        </is>
-      </c>
+          <t>2026-03-02T11:49:55</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T20260226001</t>
+          <t>T20260225002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2774,7 +2774,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:00</t>
+          <t>2026-02-25T13:01:41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:00</t>
+          <t>2026-02-25T13:01:41</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2797,20 +2797,48 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
@@ -2833,17 +2861,17 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>["data\\attachments\\T20260226001\\高鐵.pdf"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-02-26T12:05:19</t>
+          <t>2026-02-25T13:01:41</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-03-02T11:49:55</t>
+          <t>2026-03-02T16:37:45</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
@@ -2851,12 +2879,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T20260225002</t>
+          <t>T20260225001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deleted</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2865,19 +2893,35 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>施品甄</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>工作會議</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>台南 板橋</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-25T07:00:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-25T18:15:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2887,18 +2931,18 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2909,22 +2953,22 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2935,12 +2979,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"date_md": "02/25", "route": "台南 板橋", "transport_type": "高鐵", "transport_amt": 1320.0, "per_diem_amt": 0.0, "accommodation_amt": 0.0, "other_amt": 0.0, "receipt_no": ""}]</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1320.0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2949,152 +2993,20 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf"]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-02-25T13:01:41</t>
+          <t>2026-02-25T12:58:44</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-03-02T16:37:45</t>
+          <t>2026-02-25T14:58:41</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T20260225001</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>施品甄</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>115CA008</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>工作會議</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台南 板橋</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-02-25T07:00:00</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-02-25T18:15:00</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>[{"date_md": "02/25", "route": "台南 板橋", "transport_type": "高鐵", "transport_amt": 1320.0, "per_diem_amt": 0.0, "accommodation_amt": 0.0, "other_amt": 0.0, "receipt_no": ""}]</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1320.0</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>["data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf", "data\\attachments\\T20260225001\\高鐵.pdf"]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>2026-02-25T12:58:44</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:58:41</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
